--- a/QUOTATION_EXCEL_TEMPLATES/la_ch_land/LA_CH_LAND_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/la_ch_land/LA_CH_LAND_2026_QUOTATION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\다른 컴퓨터\내 컴퓨터\LK Group 관련\7. 한국-중국 VIA 라오스 운송 관련\고객 견적 확인 요청건\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\la_ch_land\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4DDA8C-483A-4F51-8B29-DD9E930F496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A48A8-1694-42C7-A851-6A259E30658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -1051,16 +1051,16 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lao-Chia 가견적</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>- 기한: 2025년 11월 말, 고객의 요청에 의하여 견적후 배송/출발 지연이 발생할 경우 운임 변동이 있을수 있으니 참고 부탁 드립니다.- 동 가견적 운임의 중량 및 크기는 단순 예상치이므로 최종 책정 방법인 기준인 실측시 금액 차이가 발생 할수 있으니, 참고용으로만 확인 부탁 드립니다.
 - 운임은 USD 기준이며, 이외 화폐는 가견적 안내시의 환율 기준이므로, 최종 운임 책정시의 환율변동으로 인한 운임 차이가 발생할수 있으니, 참고용으로만 확인 부탁 드립니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>* 모든 비용은 회사의 내규 및 각 물품의 중량/크기 실측을 기준으로 청구되며 최소 운임은 $13.4/kg 이며, 청구중량에 따라 차등 운임이 적용 됩니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lao-Chia 가견적서</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1990,6 +1990,129 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2008,128 +2131,17 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2138,18 +2150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2168,18 +2168,11 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2233,7 +2226,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$25:$F$43" spid="_x0000_s2080"/>
+                  <a14:cameraTool cellRange="$A$25:$F$43" spid="_x0000_s2083"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2497,8 +2490,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="50800" y="12369800"/>
-          <a:ext cx="8229600" cy="3733800"/>
+          <a:off x="50800" y="12465050"/>
+          <a:ext cx="8280400" cy="3727450"/>
           <a:chOff x="50800" y="15240000"/>
           <a:chExt cx="7899400" cy="3733800"/>
         </a:xfrm>
@@ -2629,8 +2622,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10261600" y="12344400"/>
-          <a:ext cx="7975600" cy="3759200"/>
+          <a:off x="10312400" y="12439650"/>
+          <a:ext cx="8020050" cy="3752850"/>
           <a:chOff x="9118600" y="15214600"/>
           <a:chExt cx="7975600" cy="3719369"/>
         </a:xfrm>
@@ -2767,8 +2760,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="20193000" y="12344399"/>
-          <a:ext cx="8026400" cy="3759201"/>
+          <a:off x="20294600" y="12439649"/>
+          <a:ext cx="8039100" cy="3752851"/>
           <a:chOff x="19761200" y="15214599"/>
           <a:chExt cx="8026400" cy="3747978"/>
         </a:xfrm>
@@ -2907,7 +2900,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1105"/>
+                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1108"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3246,47 +3239,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:Y60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="35" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.3984375" style="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" style="35" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.375" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="4" style="35" customWidth="1"/>
     <col min="8" max="8" width="15" style="35" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.59765625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.59765625" style="50" customWidth="1"/>
-    <col min="14" max="14" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.8984375" style="50" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.09765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.19921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.625" style="50" customWidth="1"/>
+    <col min="14" max="14" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.875" style="50" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.125" style="50" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.25" style="50" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="2.5" style="50" customWidth="1"/>
-    <col min="21" max="21" width="27.69921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.75" style="50" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.5" style="50" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="50" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.19921875" style="50" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.75" style="50" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="37.25" style="50" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
-      <c r="B1" s="163" t="s">
+      <c r="B1" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="H1" s="164" t="s">
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="H1" s="168" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
     </row>
     <row r="2" spans="2:25">
       <c r="B2" s="36" t="s">
@@ -3321,24 +3314,24 @@
         <f>C3+D3</f>
         <v>24000</v>
       </c>
-      <c r="H3" s="166" t="s">
+      <c r="H3" s="163" t="s">
         <v>223</v>
       </c>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
-      <c r="N3" s="166" t="s">
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="N3" s="163" t="s">
         <v>194</v>
       </c>
-      <c r="O3" s="166"/>
-      <c r="P3" s="166"/>
-      <c r="Q3" s="166"/>
-      <c r="U3" s="166" t="s">
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="U3" s="163" t="s">
         <v>195</v>
       </c>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="166"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
     </row>
     <row r="4" spans="2:25">
       <c r="B4" s="40" t="s">
@@ -3354,31 +3347,31 @@
         <f>C4+D4</f>
         <v>34</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="168"/>
-      <c r="J4" s="167" t="s">
+      <c r="I4" s="165"/>
+      <c r="J4" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="168"/>
+      <c r="K4" s="165"/>
       <c r="L4" s="50"/>
-      <c r="N4" s="167" t="s">
+      <c r="N4" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="168"/>
-      <c r="P4" s="167" t="s">
+      <c r="O4" s="165"/>
+      <c r="P4" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="168"/>
-      <c r="U4" s="167" t="s">
+      <c r="Q4" s="165"/>
+      <c r="U4" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="V4" s="168"/>
-      <c r="W4" s="167" t="s">
+      <c r="V4" s="165"/>
+      <c r="W4" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="168"/>
+      <c r="X4" s="165"/>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" s="42" t="s">
@@ -4027,12 +4020,12 @@
       <c r="Y19" s="63"/>
     </row>
     <row r="20" spans="2:25">
-      <c r="B20" s="162" t="s">
+      <c r="B20" s="166" t="s">
         <v>215</v>
       </c>
-      <c r="C20" s="162"/>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="166"/>
       <c r="H20" s="36" t="s">
         <v>46</v>
       </c>
@@ -4063,12 +4056,12 @@
       <c r="Y20" s="63"/>
     </row>
     <row r="21" spans="2:25">
-      <c r="B21" s="162" t="s">
+      <c r="B21" s="166" t="s">
         <v>280</v>
       </c>
-      <c r="C21" s="162"/>
-      <c r="D21" s="162"/>
-      <c r="E21" s="162"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
       <c r="H21" s="36" t="s">
         <v>110</v>
       </c>
@@ -4092,11 +4085,11 @@
       </c>
       <c r="R21" s="63"/>
       <c r="S21" s="63"/>
-      <c r="U21" s="165" t="s">
+      <c r="U21" s="162" t="s">
         <v>140</v>
       </c>
-      <c r="V21" s="165"/>
-      <c r="W21" s="165"/>
+      <c r="V21" s="162"/>
+      <c r="W21" s="162"/>
       <c r="X21" s="63">
         <f>SUM(X9:X20)</f>
         <v>0</v>
@@ -4189,12 +4182,12 @@
       </c>
       <c r="R24" s="63"/>
       <c r="S24" s="63"/>
-      <c r="U24" s="166" t="s">
+      <c r="U24" s="163" t="s">
         <v>196</v>
       </c>
-      <c r="V24" s="166"/>
-      <c r="W24" s="166"/>
-      <c r="X24" s="166"/>
+      <c r="V24" s="163"/>
+      <c r="W24" s="163"/>
+      <c r="X24" s="163"/>
       <c r="Y24" s="35"/>
     </row>
     <row r="25" spans="2:25">
@@ -4505,11 +4498,11 @@
       </c>
       <c r="R32" s="63"/>
       <c r="S32" s="63"/>
-      <c r="U32" s="165" t="s">
+      <c r="U32" s="162" t="s">
         <v>140</v>
       </c>
-      <c r="V32" s="165"/>
-      <c r="W32" s="165"/>
+      <c r="V32" s="162"/>
+      <c r="W32" s="162"/>
       <c r="X32" s="63">
         <f>SUM(X26:X31)</f>
         <v>0</v>
@@ -4615,12 +4608,12 @@
       </c>
       <c r="K36" s="63"/>
       <c r="L36" s="63"/>
-      <c r="N36" s="165" t="s">
+      <c r="N36" s="162" t="s">
         <v>140</v>
       </c>
-      <c r="O36" s="165"/>
-      <c r="P36" s="165"/>
-      <c r="Q36" s="165"/>
+      <c r="O36" s="162"/>
+      <c r="P36" s="162"/>
+      <c r="Q36" s="162"/>
       <c r="R36" s="52">
         <f>SUM(R9:R35)</f>
         <v>0</v>
@@ -4880,11 +4873,11 @@
       <c r="L57" s="52"/>
     </row>
     <row r="58" spans="8:12">
-      <c r="H58" s="165" t="s">
+      <c r="H58" s="162" t="s">
         <v>140</v>
       </c>
-      <c r="I58" s="165"/>
-      <c r="J58" s="165"/>
+      <c r="I58" s="162"/>
+      <c r="J58" s="162"/>
       <c r="K58" s="55">
         <f>SUM(K9:K57)</f>
         <v>0</v>
@@ -4912,6 +4905,11 @@
     </sortState>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="U21:W21"/>
     <mergeCell ref="H58:J58"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="N3:Q3"/>
@@ -4925,11 +4923,6 @@
     <mergeCell ref="U24:X24"/>
     <mergeCell ref="U32:W32"/>
     <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="U21:W21"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4945,10 +4938,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.09765625" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.125" style="56" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68" style="56" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="56"/>
   </cols>
@@ -5121,7 +5114,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5132,48 +5125,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.8984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="46.19921875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="46.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="30.8984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="30.875" style="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="23" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="36.375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="143" t="s">
-        <v>287</v>
-      </c>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
+      <c r="C1" s="132" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
       <c r="L1" s="86" t="s">
         <v>259</v>
       </c>
-      <c r="M1" s="139" t="s">
+      <c r="M1" s="128" t="s">
         <v>284</v>
       </c>
-      <c r="N1" s="140"/>
+      <c r="N1" s="129"/>
       <c r="R1" s="23">
         <f>D11</f>
         <v>1</v>
@@ -5191,7 +5184,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="22" t="s">
         <v>3</v>
       </c>
@@ -5202,22 +5195,22 @@
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="141" t="s">
+      <c r="E2" s="130" t="s">
         <v>285</v>
       </c>
-      <c r="F2" s="141"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="149" t="s">
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="115" t="s">
         <v>193</v>
       </c>
-      <c r="J2" s="150"/>
-      <c r="K2" s="151"/>
-      <c r="L2" s="158" t="s">
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="124" t="s">
         <v>247</v>
       </c>
-      <c r="M2" s="159"/>
-      <c r="N2" s="147"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="136"/>
       <c r="R2" s="24">
         <f>N16</f>
         <v>0</v>
@@ -5237,7 +5230,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
@@ -5250,12 +5243,12 @@
       <c r="F3" s="114"/>
       <c r="G3" s="114"/>
       <c r="H3" s="114"/>
-      <c r="I3" s="152"/>
-      <c r="J3" s="153"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="161"/>
-      <c r="N3" s="148"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="137"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -5274,7 +5267,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
@@ -5287,16 +5280,16 @@
       <c r="F4" s="114"/>
       <c r="G4" s="114"/>
       <c r="H4" s="114"/>
-      <c r="I4" s="155" t="s">
+      <c r="I4" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="156"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="144" t="s">
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="133" t="s">
         <v>248</v>
       </c>
-      <c r="M4" s="145"/>
-      <c r="N4" s="146"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="135"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -5312,7 +5305,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
@@ -5352,7 +5345,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="22">
         <v>1</v>
       </c>
@@ -5395,7 +5388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="22">
         <v>2</v>
       </c>
@@ -5413,7 +5406,7 @@
       <c r="M7" s="21"/>
       <c r="N7" s="8"/>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="22">
         <v>3</v>
       </c>
@@ -5431,7 +5424,7 @@
       <c r="M8" s="21"/>
       <c r="N8" s="8"/>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="22">
         <v>4</v>
       </c>
@@ -5449,7 +5442,7 @@
       <c r="M9" s="21"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="22">
         <v>5</v>
       </c>
@@ -5467,7 +5460,7 @@
       <c r="M10" s="21"/>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A11" s="114" t="s">
         <v>14</v>
       </c>
@@ -5495,21 +5488,21 @@
       <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="156" t="s">
         <v>226</v>
       </c>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115" t="s">
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156" t="s">
         <v>227</v>
       </c>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="115"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
       <c r="L12" s="114" t="s">
         <v>15</v>
       </c>
@@ -5520,20 +5513,20 @@
       </c>
       <c r="P12" s="23"/>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A13" s="116" t="s">
-        <v>288</v>
-      </c>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A13" s="157" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
       <c r="L13" s="87" t="s">
         <v>16</v>
       </c>
@@ -5546,18 +5539,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A14" s="115"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A14" s="156"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="159"/>
+      <c r="K14" s="159"/>
       <c r="L14" s="87" t="s">
         <v>260</v>
       </c>
@@ -5570,18 +5563,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A15" s="115"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="159"/>
+      <c r="I15" s="159"/>
+      <c r="J15" s="159"/>
+      <c r="K15" s="159"/>
       <c r="L15" s="87" t="s">
         <v>261</v>
       </c>
@@ -5595,18 +5588,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="115"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="119" t="s">
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="159"/>
+      <c r="G16" s="159"/>
+      <c r="H16" s="159"/>
+      <c r="I16" s="159"/>
+      <c r="J16" s="159"/>
+      <c r="K16" s="159"/>
+      <c r="L16" s="160" t="s">
         <v>228</v>
       </c>
       <c r="M16" s="88" t="s">
@@ -5618,18 +5611,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="115"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="120"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="159"/>
+      <c r="G17" s="159"/>
+      <c r="H17" s="159"/>
+      <c r="I17" s="159"/>
+      <c r="J17" s="159"/>
+      <c r="K17" s="159"/>
+      <c r="L17" s="161"/>
       <c r="M17" s="89" t="s">
         <v>18</v>
       </c>
@@ -5639,18 +5632,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="120"/>
+      <c r="A18" s="156"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="159"/>
+      <c r="G18" s="159"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="159"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="159"/>
+      <c r="L18" s="161"/>
       <c r="M18" s="90" t="s">
         <v>19</v>
       </c>
@@ -5659,19 +5652,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A19" s="117"/>
-      <c r="B19" s="117"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="120"/>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A19" s="158"/>
+      <c r="B19" s="158"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="159"/>
+      <c r="L19" s="161"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -5696,66 +5689,66 @@
       <c r="M20" s="92"/>
       <c r="N20" s="92"/>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A21" s="122" t="s">
-        <v>289</v>
-      </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="122"/>
-      <c r="M21" s="122"/>
-      <c r="N21" s="122"/>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A22" s="123" t="s">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A21" s="139" t="s">
+        <v>288</v>
+      </c>
+      <c r="B21" s="139"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="139"/>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A22" s="140" t="s">
         <v>230</v>
       </c>
-      <c r="B22" s="123"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="123"/>
-      <c r="H22" s="123"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="123"/>
-      <c r="M22" s="123"/>
-      <c r="N22" s="123"/>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A23" s="123"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="123"/>
-      <c r="M23" s="123"/>
-      <c r="N23" s="123"/>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A24" s="124" t="s">
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="140"/>
+      <c r="N22" s="140"/>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A23" s="140"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="140"/>
+      <c r="N23" s="140"/>
+    </row>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A24" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="125"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="132"/>
+      <c r="B24" s="142"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="148"/>
+      <c r="E24" s="149"/>
       <c r="F24" s="26"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
@@ -5764,75 +5757,75 @@
       <c r="K24" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="121"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A25" s="126"/>
-      <c r="B25" s="127"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="134"/>
-      <c r="E25" s="135"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="138"/>
+      <c r="N24" s="138"/>
+    </row>
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A25" s="143"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="151"/>
+      <c r="E25" s="152"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="114"/>
-      <c r="L25" s="121"/>
-      <c r="M25" s="121"/>
-      <c r="N25" s="121"/>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A26" s="126"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="138"/>
+    </row>
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A26" s="143"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="150"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="152"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="114"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="121"/>
-      <c r="N26" s="121"/>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="133"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="135"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="138"/>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A27" s="143"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="152"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="114"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="121"/>
-      <c r="N27" s="121"/>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A28" s="128"/>
-      <c r="B28" s="129"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="138"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="138"/>
+      <c r="N27" s="138"/>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A28" s="145"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="155"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="114"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="121"/>
-      <c r="N28" s="121"/>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="30">
+      <c r="L28" s="138"/>
+      <c r="M28" s="138"/>
+      <c r="N28" s="138"/>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="16"/>
@@ -5848,7 +5841,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="30">
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -5868,8 +5861,8 @@
     <row r="32" spans="1:14" ht="16.5" customHeight="1"/>
     <row r="33" spans="17:22" ht="16.5" customHeight="1"/>
     <row r="34" spans="17:22" ht="16.5" customHeight="1"/>
-    <row r="37" spans="17:22" ht="24.9" customHeight="1"/>
-    <row r="38" spans="17:22" ht="24.9" customHeight="1">
+    <row r="37" spans="17:22" ht="24.95" customHeight="1"/>
+    <row r="38" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q38" s="18"/>
       <c r="R38" s="18"/>
       <c r="S38" s="18"/>
@@ -5877,28 +5870,28 @@
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
     </row>
-    <row r="39" spans="17:22" ht="24.9" customHeight="1">
+    <row r="39" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q39" s="19"/>
     </row>
-    <row r="40" spans="17:22" ht="24.9" customHeight="1">
+    <row r="40" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q40" s="19"/>
     </row>
-    <row r="41" spans="17:22" ht="24.9" customHeight="1">
+    <row r="41" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q41" s="19"/>
     </row>
-    <row r="42" spans="17:22" ht="24.9" customHeight="1">
+    <row r="42" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q42" s="19"/>
     </row>
-    <row r="43" spans="17:22" ht="24.9" customHeight="1">
+    <row r="43" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q43" s="19"/>
     </row>
-    <row r="44" spans="17:22" ht="24.9" customHeight="1">
+    <row r="44" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q44" s="19"/>
     </row>
-    <row r="45" spans="17:22" ht="24.9" customHeight="1">
+    <row r="45" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q45" s="19"/>
     </row>
-    <row r="46" spans="17:22" ht="24.9" customHeight="1">
+    <row r="46" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q46" s="19"/>
     </row>
     <row r="47" spans="17:22" ht="30" customHeight="1"/>
@@ -5919,12 +5912,19 @@
     <row r="62" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="K24:K28"/>
+    <mergeCell ref="L24:N28"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A24:B28"/>
+    <mergeCell ref="C24:E28"/>
+    <mergeCell ref="A23:N23"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:H2"/>
@@ -5932,23 +5932,16 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="K24:K28"/>
-    <mergeCell ref="L24:N28"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A24:B28"/>
-    <mergeCell ref="C24:E28"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>N6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5958,7 +5951,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="27" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -5967,25 +5960,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U49"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.09765625" style="56" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8984375" style="79" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.8984375" style="79" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.3984375" style="79" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.3984375" style="79" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.3984375" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="56" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.875" style="79" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="79" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" style="79" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" style="79" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.375" style="56" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.75" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
